--- a/2022 data/excel_outputs/21_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/21_boothwise_data.xlsx
@@ -14,690 +14,1065 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="375">
   <si>
     <t>AC 21 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>####0##0 ####### ### #### #</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### #### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ###### #### ####### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### ###### #### ####### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #### 2</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ##### #### 1</t>
-  </si>
-  <si>
-    <t>##### ##### ##0##0 ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ###### #### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #####</t>
-  </si>
-  <si>
-    <t>####0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ####</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ## #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ## #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ###### ## #### 3</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ##### #### 1</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ##### #### 2</t>
-  </si>
-  <si>
-    <t>######## ####### #####</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ####</t>
-  </si>
-  <si>
-    <t>####0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### #####</t>
-  </si>
-  <si>
-    <t>###### ## ######## #### #### #####</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## #### 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ## #### 4</t>
-  </si>
-  <si>
-    <t>##### ## ##### ##### #### ## #### 1</t>
-  </si>
-  <si>
-    <t>##### ## ##### ##### #### ## #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######### #### 2R</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### 3</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### 4</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### 5</t>
-  </si>
-  <si>
-    <t>##0##0#0##0 ###### #### 6</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 1</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 2</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 3</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 4</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 5</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 6</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 7</t>
-  </si>
-  <si>
-    <t>#### ##### #### #0##0 ###### #### 8</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ##### ###### #### 1</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ##### ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ######## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ######## #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ########### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### ########### #### 2</t>
-  </si>
-  <si>
-    <t>####### ###### #### ###### ##0##0##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ######### ##### #### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ####### #### 4</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ####</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ###### ####</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ######</t>
-  </si>
-  <si>
-    <t>#### ##### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ########### ###### #### 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ########### ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ###### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######### ###</t>
-  </si>
-  <si>
-    <t>#0##0##0##0 ########</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ########### #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### #########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### ###### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### ###### #### 2</t>
-  </si>
-  <si>
-    <t>######### #0##0##0 ##### #########</t>
-  </si>
-  <si>
-    <t>####0##0 #########</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #######</t>
-  </si>
-  <si>
-    <t>##0##0##0 #####</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ####### #### 2</t>
-  </si>
-  <si>
-    <t>###### ########### ##0##0##### ########### #### 1</t>
-  </si>
-  <si>
-    <t>###### ########### ##0##0##### ########### #### 2</t>
-  </si>
-  <si>
-    <t>###### ########### ##0##0##### ########### #### 3</t>
-  </si>
-  <si>
-    <t>####0##0 ############</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ######## ### #### 3</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####### ##### ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####### ##### ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 #### ####### ##### ##### #### 3</t>
-  </si>
-  <si>
-    <t>##0#0 ######## ##### #### 1</t>
-  </si>
-  <si>
-    <t>##0#0 ######## ##### #### 2</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### #### ##0 4</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### #### ##0 5</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### ####.6</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### ####.7</t>
-  </si>
-  <si>
-    <t>##### ###### #### ###### ##### ##### ##### #### ##0 8</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ##### ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ##### ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ##### ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ##### ##### #### ##0 4</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ##### ##### #### ##0 5</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ##### ##### #### ##0 6</t>
-  </si>
-  <si>
-    <t>### #### ###### ##### ##### ##### #### ##0 7</t>
-  </si>
-  <si>
-    <t>####### #### #### ##### ##### ##### ####.1</t>
-  </si>
-  <si>
-    <t>####### #### #### ##### ##### ##### ####.2</t>
-  </si>
-  <si>
-    <t>####### #### #### ##### ##### ##### ####.3</t>
-  </si>
-  <si>
-    <t>####### #### #### ##### ##### ##### ####.4</t>
-  </si>
-  <si>
-    <t>####### #### #### ##### ##### ##### ####.5</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### ##0 3</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##### #### 4</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ##### ##### ##### #### 1</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ##### ##### ##### #### 2</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ##### ##### ##### #### 3</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ##### ##### ##### #### 4</t>
-  </si>
-  <si>
-    <t>##### ####### ######## ##### ##### ##### #### 5</t>
-  </si>
-  <si>
-    <t>##0##0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 #########</t>
-  </si>
-  <si>
-    <t>##### ####### #######</t>
-  </si>
-  <si>
-    <t>####0##0 ## #######</t>
-  </si>
-  <si>
-    <t>####0##0 #### ########</t>
-  </si>
-  <si>
-    <t>#### ####0##0 #### ######## #### 1</t>
-  </si>
-  <si>
-    <t>#### ####0##0 #### ######## #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ###### ########</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ########### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ########### #### 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 #######</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ### #### 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ####### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ########## ####### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ########### ###</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ####### ######</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ####.1</t>
-  </si>
-  <si>
-    <t>####0##0 ###### #### ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ######## #### 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ######## #### 2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ######## #### 3</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ######</t>
-  </si>
-  <si>
-    <t>##### #0##0 #### #### 1</t>
-  </si>
-  <si>
-    <t>##### #0##0 #### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ##### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ##### #### 2</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ##### ##### #### 3</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ######## ####.1</t>
-  </si>
-  <si>
-    <t>##### ######## ######## ######## ####.2</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######### #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ####### ######### #### 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 #### ########## #### 1</t>
-  </si>
-  <si>
-    <t>##### ##0##0 #### ########## #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 ##0### ####</t>
-  </si>
-  <si>
-    <t>###### ## #### ###</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### ### #### 1</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### ### #### 2</t>
-  </si>
-  <si>
-    <t>##0##0##0 #### ### #### 3</t>
-  </si>
-  <si>
-    <t>#### #0##0 ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### #0##0 ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### #0##0 ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######## #### 1</t>
-  </si>
-  <si>
-    <t>####0##0 ##### ######## #### 2</t>
-  </si>
-  <si>
-    <t>##### ##0##0 ####### ######</t>
-  </si>
-  <si>
-    <t>##### #0##0 ##### #### 1</t>
-  </si>
-  <si>
-    <t>##### #0##0 ##### #### 2</t>
+    <t>PRA0VI0 PHARIDAPUR MAN KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHARIDAPUR MAN KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ILAYACHIPUR KHADAGU KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ILAYACHIPUR KHADAGU KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KASAMAPUR KRRIPARAM URPH SAMUDARAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GOPALAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 SIHORA GIRADHAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ABDULAPUR MUNNA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 PHARIDAPUR SAMSARU URPH DHOKALAPUR KAKSH 1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 PHARIDAPUR SAMSARU URPH DHOKALAPUR KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHARIDAPUR DARGA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ISLAMAPUR THAMBUCHAU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BARUKI PRATHAM KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BARUKI PRATHAM KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BARUKI PRATHAM KAKSH 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ISLAMAPUR LALU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHATEHAPUR ASAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUJAPHPHARABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAMGODA SHEKH KAKSH N0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GAMGODA SHEKH KAKSH N0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AHAMADAPUR CHANDURU URPH GADANA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KANHA NAMGALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RUKANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR KHANDASAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAKAR NAMGALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHAPUR SAIDU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHARIDAPUR NIJAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GUJARAPUR JASAPAL</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 GAMGODA JAT KAKSH 1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 GAMGODA JAT KAKSH 2</t>
+  </si>
+  <si>
+    <t>K0PU0MA0VI0 DHANAURA</t>
+  </si>
+  <si>
+    <t>PAMCHAYATAGHAR PHARIDAPUR DALLU</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 UMARI KAKSH 1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 UMARI KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UMARI KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 UMARI KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAHAMUDAPUR JAGAMAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHANAURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAMDA NAMGALI KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAMDA NAMGALI KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ISSAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHEDAKI TAPPA, NAMGAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TARIKAMAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BILARI KAKSH 1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BILARI KAKSH 2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 BILARI KAKSH 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAGAL JAT KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAGAL JAT KAKSH 2</t>
+  </si>
+  <si>
+    <t>NAGAL JAT INTAR KALEJ NAGAL JAT</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BALIDAYA KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BALIDAYA KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BISATH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 INAMAPURA KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 INAMAPURA KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KUKADA ISLAMAPUR KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KUKADA ISLAMAPUR KAKSH 2</t>
+  </si>
+  <si>
+    <t>SI0DI0I0KA0 HALDAUR KAKSH 1</t>
+  </si>
+  <si>
+    <t>SI0DI0I0KA0 HALDAUR KAKSH 2</t>
+  </si>
+  <si>
+    <t>SI0DI0I0KA0 HALDAUR KAKSH 3</t>
+  </si>
+  <si>
+    <t>SI0DI0I0KA0 HALDAUR KAKSH 4</t>
+  </si>
+  <si>
+    <t>SI0DI0I0KA0 HALDAUR KAKSH 5</t>
+  </si>
+  <si>
+    <t>SI0DI0I0KA0 HALDAUR KAKSH 6</t>
+  </si>
+  <si>
+    <t>RAJA HARAVAMSH SIMH I0KA0 HALDAUR KAKSH 1</t>
+  </si>
+  <si>
+    <t>RAJA HARAVAMSH SIMH I0KA0 HALDAUR KAKSH 2</t>
+  </si>
+  <si>
+    <t>RAJA HARAVAMSH SIMH I0KA0 HALDAUR KAKSH 3</t>
+  </si>
+  <si>
+    <t>RAJA HARAVAMSH SIMH I0KA0 HALDAUR KAKSH 4</t>
+  </si>
+  <si>
+    <t>RAJA HARAVAMSH SIMH I0KA0 HALDAUR KAKSH 5</t>
+  </si>
+  <si>
+    <t>RAJA HARAVAMSH SIMH I0KA0 HALDAUR KAKSH 6</t>
+  </si>
+  <si>
+    <t>K0PU0MA0VI0 SKUL HALDAUR KAKSH 1</t>
+  </si>
+  <si>
+    <t>K0PU0MA0VI0 SKUL HALDAUR KAKSH 2</t>
+  </si>
+  <si>
+    <t>K0PU0MA0VI0 SKUL HALDAUR KAKSH 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ATAPUR URPH KHATAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NASIRAPUR NAIN SIMH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHARIDAPUR SADHIRAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARADASAPUR JAPHARABAD KAKSH N0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARADASAPUR JAPHARABAD KAKSH N0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KUNDA BAGAIN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR URPH KUMHARAPURA KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR URPH KUMHARAPURA KAKSH 2</t>
+  </si>
+  <si>
+    <t>MAHARANA PRATAP VIDYA MANIDAR JU0HA0SKUL GOGALI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHERAPUR KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHERAPUR KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PUTTHA KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PUTTHA KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHELI GUJAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHAIRAPUR PARATAPAPUR SITHAT DHELA GUJJAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JALALAPUR HASANA KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JALALAPUR HASANA KAKSH 2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 AMHEDA KAKSH 1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 AMHEDA KAKSH 2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 AMHEDA KAKSH 3</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAJUPURA SAID</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SULTANAPUR ABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHANAGAR KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHANAGAR KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAPHIPUR HIRA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHADIPUR KALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SALLAHAPUR KAKSH 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SALLAHAPUR KAKSH 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MITHAN KUVAMR PRATAP SIMH</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 NAMGALI SHAPHIPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHAIRABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LADANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ASADAG.DH</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KAKARALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RUGADI SAID</t>
+  </si>
+  <si>
+    <t>JANATA INTAR KALEJ MAHUA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SUNAPATA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAMIDAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AKABARAPUR DEVAMAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 ALHAIDADAPUR MUBARAK</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALIPUR DAMODAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHULASANDA KHAKAM KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHULASANDA KHAKAM KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHULASANDA HIRA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHOSAPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RUSTAMAPUR SHER</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PALIJAT</t>
+  </si>
+  <si>
+    <t>K0PU0MA0VI0 KAJIPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MOMINAPUR GILA.DI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NARAGADI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHAKAULI</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 PHULASANDA HIRA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR SADHO KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR SADHO KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NIJATAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SALARAPUR SHAPHAKKATAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TAKIPURA PURAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAHAKARAMAPUR GILA.DA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TAHARAPUR TAPPA NAMGAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KARIMAPUR MUBARAK</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHEDIJAT</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 SIKARI BAJURG</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAHAMUDAPUR BHIAKKA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BILASAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHARIDABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BEGARAJAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI BEGARAJAPUR</t>
+  </si>
+  <si>
+    <t>KAMOTAR K0JU0HA0SKUL BEGARAJAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIKARI KHURD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAGHUNATHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NURAPUR KHE.DAKI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KISHANAPUR BHOGAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NASIRAPUR BUJURG</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JARIPHAPUR CHATAR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 PADALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DHIMGARAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAHAMUDAPUR MILAK</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SIKANDARAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SADIKABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SALEMAPUR RUKHADIYO</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MEHARAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BASAVANAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAMASABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHAJURA JAT</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PAPASARA KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PAPASARA KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAIH.DAPUR</t>
+  </si>
+  <si>
+    <t>SVAMI PRERANANANAD JU0HA0SKUL SADARUDDINANAGAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMABAD</t>
+  </si>
+  <si>
+    <t>़68PRA0VI0 AMARABAD</t>
+  </si>
+  <si>
+    <t>KANYA PATHASHALA BAIRAMABAD G.DHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAY KAJIYAN DEHAT NAHATAUR KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAY KAJIYAN DEHAT NAHATAUR KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SARAY KAJIYAN DEHAT NAHATAUR KAKSH-3</t>
+  </si>
+  <si>
+    <t>VI0KH0 KARYALAY NAHATAUR</t>
+  </si>
+  <si>
+    <t>SHYAM NARAYAN SI.NH SMARAK INTAR KALEJ NAHATAUR KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>SHYAM NARAYAN SI.NH SMARAK INTAR KALEJ NAHATAUR KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>SHYAM NARAYAN SI.NH SMARAK INTAR KALEJ NAHATAUR KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>SHYAM NARAYAN SI.NH SMARAK INTAR KALEJ NAHATAUR KAKSH NAM0 4</t>
+  </si>
+  <si>
+    <t>SHYAM NARAYAN SI.NH SMARAK INTAR KALEJ NAHATAUR KAKSH NAM0 5</t>
+  </si>
+  <si>
+    <t>JAIN VIDHA MANIDAR INTAR KALEJ NAHATAUR KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>JAIN VIDHA MANIDAR INTAR KALEJ NAHATAUR KAKSH NAM0 2</t>
+  </si>
+  <si>
+    <t>JAIN VIDHA MANIDAR INTAR KALEJ NAHATAUR KAKSH NAM0 3</t>
+  </si>
+  <si>
+    <t>JAIN VIDHA MANIDAR INTAR KALEJ NAHATAUR KAKSH NAM0 4</t>
+  </si>
+  <si>
+    <t>JAIN VIDHA MANIDAR INTAR KALEJ NAHATAUR KAKSH NAM0 5</t>
+  </si>
+  <si>
+    <t>JAIN VIDHA MANIDAR INTAR KALEJ NAHATAUR KAKSH NAM0 6</t>
+  </si>
+  <si>
+    <t>RAJAKIY KANYA INTAR KALEJ NAHATAUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAHATAUR KAKSH SAM0 1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAHATAUR KAKSH SAM0 2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NAHATAUR KAKSH SAM0 3</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 NAHATAUR KAKSH-1</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 NAHATAUR KAKSH-2</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 NAHATAUR KAKSH-3</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 NAHATAUR KAKSH-4</t>
+  </si>
+  <si>
+    <t>KISAN SEVA SAH0SAMITI NAHATAUR, UTTARI</t>
+  </si>
+  <si>
+    <t>HAPHIZ MAUHAMMAD IBRAHIM INTAR KALEJ NAHATAUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SADATANAGAR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 KHIAJARAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KUMARARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHEKHAPUR LALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUSTAPHABAD</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 NARAYANAKHE.DI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MIMALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAYAPUR LAK.DA</t>
+  </si>
+  <si>
+    <t>KANYA PATHASHALA NAKIBAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MURASHADAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHALAUDI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAK GOVARDHAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHERAPUR BALLA</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 PUTTHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ABDUL KHALIKAPUR BALARAM</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MILAK MUKIMAPUR</t>
+  </si>
+  <si>
+    <t>ABHIANAV PURV MA0VI0 MILAK MUKIMAPUR KAKSH NAM0 1</t>
+  </si>
+  <si>
+    <t>ABHIANAV PURV MA0VI0 MILAK MUKIMAPUR KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAYAPUR MALIYABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KASHMIRI ABUNASIRAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AMINABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHALOAIDA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MARUPHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 VAJIDAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ILAHABAD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AMBARAPUR JAPHAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUJAPHAPHARAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 DHANUPURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BAIRAMAPUR KHAJURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HUSAINAPUR SAMASAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHETAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 GARAVAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHARAKHE.DI URPH DUGARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MANDAURA VIP</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAMDAURI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAJAHARAPUR</t>
+  </si>
+  <si>
+    <t>JANATA INTAR KALEJ AMKU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MEHARALIPUR (DHANUPURA) KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MEHARALIPUR (DHANUPURA) KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NANHE.DA KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 NANHE.DA KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TURABANAGAR</t>
+  </si>
+  <si>
+    <t>CHA0NEHARU SMARAK I0KA0 BALAPUR AKHE.DA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KHANDASAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TAHARAPUR SAID</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUKARRABAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MALAKAPUR</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SEDHA KAKSH-1</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SEDHA KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 IBRAHIMAPUR LAL</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BASEDA KHEMACHAND</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SEDHI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BERAKHE.DA CHAIHAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 TAPARAULA</t>
+  </si>
+  <si>
+    <t>ABHIANAV JU0HA0SKUL NASIBAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BU.DHAPUR</t>
+  </si>
+  <si>
+    <t>K0PA0 SHADIPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DABATHALA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AKHE.DA</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 RAMAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 DABAKHE.DI SALAR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JALALAPUR ASARA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 AKABARAPUR GARAV</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MUSSEPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PHAJALALIPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 JASAMAURA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAKARAMDAPUR MANAK</t>
+  </si>
+  <si>
+    <t>PRA0VI0 RAYAPUR MALUK</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 BASE.DA NARAYAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BASE.DA UBAR</t>
+  </si>
+  <si>
+    <t>JANATA INTAR KALEJ DHAKKA KARMACHAND KAKSH-1</t>
+  </si>
+  <si>
+    <t>JANATA INTAR KALEJ DHAKKA KARMACHAND KAKSH-2</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KANDAKHE.DI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MIRJAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MATAURA DARGA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HARAGANAPUR</t>
+  </si>
+  <si>
+    <t>PURV MA0VI0 SIJAULI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SAHANAPUR NAVADA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALINAGAR PALANI KAKSH-1</t>
+  </si>
+  <si>
+    <t>PRA0VI0 ALINAGAR PALANI KAKSH-2</t>
+  </si>
+  <si>
+    <t>ADARSH I0KA0 UMARI</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PADALI MAMDU DVITIY</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PADALI MAMDU</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MATAURAMAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHATIYANA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 KIRARAKHEDI</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 MILAK</t>
+  </si>
+  <si>
+    <t>PRA0VI0 HAKIMAPUR CHANDAN</t>
+  </si>
+  <si>
+    <t>PRA0VI0 PIPALASANA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 MAU0PUR PARAMA</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 ATHARI SHEKH</t>
+  </si>
+  <si>
+    <t>JANATA I0KA0 BASE.DA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BASE.DA KHURD</t>
+  </si>
+  <si>
+    <t>PRA0VI0 BHAVANIPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHAPPAR SHIAKOHAPUR</t>
+  </si>
+  <si>
+    <t>PRA0VI0 LATIPHULLAPUR</t>
+  </si>
+  <si>
+    <t>PU0MA0VI0 HAKIMAPUR</t>
+  </si>
+  <si>
+    <t>GA.CDHI I0KA0MANAKUA</t>
+  </si>
+  <si>
+    <t>GAMDHI I0KA0 MANAKUA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 MAU0ALIPUR MUKTA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 SHEKHAPURA PITTHA</t>
+  </si>
+  <si>
+    <t>PRA0VI0 CHAKARAPUR</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM NO. 319</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM NO. 320</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM NO. 321</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM NO. 322</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM NO. 323</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM NO. 324</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 325</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 326</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 327</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 328</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 329</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 330</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 331</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 332</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 333</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 334</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 335</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 336</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 337</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 338</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 339</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 340</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 341</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 342</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 343</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 344</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 345</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 346</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 347</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 348</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 349</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 350</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 351</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 352</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 353</t>
+  </si>
+  <si>
+    <t>PRA0 VI0 DAULATAPUR SUKKHA ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM ROOM NO. 354</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -770,8 +1145,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -787,7 +1170,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -795,12 +1178,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1099,82 +1500,151 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:24">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="C2" t="s">
-        <v>228</v>
+        <v>353</v>
       </c>
       <c r="D2" t="s">
-        <v>229</v>
+        <v>354</v>
       </c>
       <c r="E2" t="s">
-        <v>230</v>
+        <v>355</v>
       </c>
       <c r="F2" t="s">
-        <v>231</v>
+        <v>356</v>
       </c>
       <c r="G2" t="s">
-        <v>232</v>
+        <v>357</v>
       </c>
       <c r="H2" t="s">
-        <v>233</v>
+        <v>358</v>
       </c>
       <c r="I2" t="s">
-        <v>234</v>
+        <v>359</v>
       </c>
       <c r="J2" t="s">
-        <v>235</v>
+        <v>360</v>
       </c>
       <c r="K2" t="s">
-        <v>236</v>
+        <v>361</v>
       </c>
       <c r="L2" t="s">
-        <v>237</v>
+        <v>362</v>
       </c>
       <c r="M2" t="s">
-        <v>238</v>
+        <v>363</v>
       </c>
       <c r="N2" t="s">
-        <v>239</v>
+        <v>364</v>
       </c>
       <c r="O2" t="s">
-        <v>240</v>
+        <v>365</v>
       </c>
       <c r="P2" t="s">
-        <v>241</v>
+        <v>366</v>
       </c>
       <c r="Q2" t="s">
-        <v>242</v>
+        <v>367</v>
       </c>
       <c r="R2" t="s">
-        <v>243</v>
+        <v>368</v>
       </c>
       <c r="S2" t="s">
-        <v>244</v>
+        <v>369</v>
       </c>
       <c r="T2" t="s">
-        <v>245</v>
+        <v>370</v>
       </c>
       <c r="U2" t="s">
-        <v>246</v>
+        <v>371</v>
       </c>
       <c r="V2" t="s">
-        <v>247</v>
+        <v>372</v>
       </c>
       <c r="W2" t="s">
-        <v>248</v>
+        <v>373</v>
       </c>
       <c r="X2" t="s">
-        <v>249</v>
+        <v>374</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1182,7 +1652,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>26</v>
       </c>
       <c r="C3">
         <v>930</v>
@@ -1256,7 +1726,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="C4">
         <v>722</v>
@@ -1330,7 +1800,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="C5">
         <v>932</v>
@@ -1404,7 +1874,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="C6">
         <v>785</v>
@@ -1478,7 +1948,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="C7">
         <v>966</v>
@@ -1552,7 +2022,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>1039</v>
@@ -1626,7 +2096,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>701</v>
@@ -1700,7 +2170,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>527</v>
@@ -1774,7 +2244,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>33</v>
       </c>
       <c r="C11">
         <v>625</v>
@@ -1848,7 +2318,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>34</v>
       </c>
       <c r="C12">
         <v>893</v>
@@ -1922,7 +2392,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C13">
         <v>1185</v>
@@ -1996,7 +2466,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="C14">
         <v>918</v>
@@ -2070,7 +2540,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>1153</v>
@@ -2144,7 +2614,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>754</v>
@@ -2218,7 +2688,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>17</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>1249</v>
@@ -2292,7 +2762,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>1195</v>
@@ -2366,7 +2836,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>724</v>
@@ -2440,7 +2910,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>769</v>
@@ -2514,7 +2984,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>933</v>
@@ -2588,7 +3058,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>22</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>695</v>
@@ -2662,7 +3132,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="C23">
         <v>549</v>
@@ -2736,7 +3206,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>958</v>
@@ -2810,7 +3280,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>25</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>801</v>
@@ -2884,7 +3354,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>854</v>
@@ -2958,7 +3428,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="C27">
         <v>491</v>
@@ -3032,7 +3502,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C28">
         <v>407</v>
@@ -3106,7 +3576,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C29">
         <v>1119</v>
@@ -3180,7 +3650,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C30">
         <v>686</v>
@@ -3254,7 +3724,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="C31">
         <v>675</v>
@@ -3328,7 +3798,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>15</v>
+        <v>54</v>
       </c>
       <c r="C32">
         <v>1092</v>
@@ -3402,7 +3872,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>15</v>
+        <v>55</v>
       </c>
       <c r="C33">
         <v>467</v>
@@ -3476,7 +3946,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C34">
         <v>764</v>
@@ -3550,7 +4020,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>619</v>
@@ -3624,7 +4094,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>819</v>
@@ -3698,7 +4168,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>716</v>
@@ -3772,7 +4242,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>559</v>
@@ -3846,7 +4316,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>490</v>
@@ -3920,7 +4390,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>1047</v>
@@ -3994,7 +4464,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>945</v>
@@ -4068,7 +4538,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>1014</v>
@@ -4142,7 +4612,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>941</v>
@@ -4216,7 +4686,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>439</v>
@@ -4290,7 +4760,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>605</v>
@@ -4364,7 +4834,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>1137</v>
@@ -4438,7 +4908,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>18</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>657</v>
@@ -4512,7 +4982,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>1081</v>
@@ -4586,7 +5056,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>814</v>
@@ -4660,7 +5130,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="C50">
         <v>484</v>
@@ -4734,7 +5204,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="C51">
         <v>785</v>
@@ -4808,7 +5278,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>48</v>
+        <v>74</v>
       </c>
       <c r="C52">
         <v>763</v>
@@ -4882,7 +5352,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="C53">
         <v>960</v>
@@ -4956,7 +5426,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>50</v>
+        <v>76</v>
       </c>
       <c r="C54">
         <v>774</v>
@@ -5030,7 +5500,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>51</v>
+        <v>77</v>
       </c>
       <c r="C55">
         <v>633</v>
@@ -5104,7 +5574,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="C56">
         <v>669</v>
@@ -5178,7 +5648,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="C57">
         <v>719</v>
@@ -5252,7 +5722,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>54</v>
+        <v>80</v>
       </c>
       <c r="C58">
         <v>765</v>
@@ -5326,7 +5796,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>55</v>
+        <v>81</v>
       </c>
       <c r="C59">
         <v>709</v>
@@ -5400,7 +5870,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>56</v>
+        <v>82</v>
       </c>
       <c r="C60">
         <v>1171</v>
@@ -5474,7 +5944,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>57</v>
+        <v>83</v>
       </c>
       <c r="C61">
         <v>1166</v>
@@ -5548,7 +6018,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>43</v>
+        <v>84</v>
       </c>
       <c r="C62">
         <v>1025</v>
@@ -5622,7 +6092,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>1109</v>
@@ -5696,7 +6166,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="C64">
         <v>811</v>
@@ -5770,7 +6240,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="C65">
         <v>909</v>
@@ -5844,7 +6314,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C66">
         <v>990</v>
@@ -5918,7 +6388,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="C67">
         <v>1048</v>
@@ -5992,7 +6462,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="C68">
         <v>885</v>
@@ -6066,7 +6536,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
       <c r="C69">
         <v>980</v>
@@ -6140,7 +6610,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="C70">
         <v>898</v>
@@ -6214,7 +6684,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="C71">
         <v>820</v>
@@ -6288,7 +6758,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="C72">
         <v>632</v>
@@ -6362,7 +6832,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>66</v>
+        <v>95</v>
       </c>
       <c r="C73">
         <v>668</v>
@@ -6436,7 +6906,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="C74">
         <v>694</v>
@@ -6510,7 +6980,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>68</v>
+        <v>97</v>
       </c>
       <c r="C75">
         <v>714</v>
@@ -6584,7 +7054,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="C76">
         <v>665</v>
@@ -6658,7 +7128,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="C77">
         <v>720</v>
@@ -6732,7 +7202,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>71</v>
+        <v>100</v>
       </c>
       <c r="C78">
         <v>703</v>
@@ -6806,7 +7276,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="C79">
         <v>1001</v>
@@ -6880,7 +7350,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="C80">
         <v>723</v>
@@ -6954,7 +7424,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>74</v>
+        <v>103</v>
       </c>
       <c r="C81">
         <v>850</v>
@@ -7028,7 +7498,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="C82">
         <v>888</v>
@@ -7102,7 +7572,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>76</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>778</v>
@@ -7176,7 +7646,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>764</v>
@@ -7250,7 +7720,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>78</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>629</v>
@@ -7324,7 +7794,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="C86">
         <v>616</v>
@@ -7398,7 +7868,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="C87">
         <v>1013</v>
@@ -7472,7 +7942,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>15</v>
+        <v>110</v>
       </c>
       <c r="C88">
         <v>800</v>
@@ -7546,7 +8016,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>81</v>
+        <v>111</v>
       </c>
       <c r="C89">
         <v>1018</v>
@@ -7620,7 +8090,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="C90">
         <v>756</v>
@@ -7694,7 +8164,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="C91">
         <v>615</v>
@@ -7768,7 +8238,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="C92">
         <v>1062</v>
@@ -7842,7 +8312,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>84</v>
+        <v>115</v>
       </c>
       <c r="C93">
         <v>935</v>
@@ -7916,7 +8386,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="C94">
         <v>416</v>
@@ -7990,7 +8460,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="C95">
         <v>883</v>
@@ -8064,7 +8534,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>87</v>
+        <v>118</v>
       </c>
       <c r="C96">
         <v>616</v>
@@ -8138,7 +8608,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>88</v>
+        <v>119</v>
       </c>
       <c r="C97">
         <v>801</v>
@@ -8212,7 +8682,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>89</v>
+        <v>120</v>
       </c>
       <c r="C98">
         <v>592</v>
@@ -8286,7 +8756,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="C99">
         <v>415</v>
@@ -8360,7 +8830,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="C100">
         <v>733</v>
@@ -8434,7 +8904,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>92</v>
+        <v>123</v>
       </c>
       <c r="C101">
         <v>831</v>
@@ -8508,7 +8978,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>93</v>
+        <v>124</v>
       </c>
       <c r="C102">
         <v>322</v>
@@ -8582,7 +9052,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="C103">
         <v>1209</v>
@@ -8656,7 +9126,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>95</v>
+        <v>125</v>
       </c>
       <c r="C104">
         <v>864</v>
@@ -8730,7 +9200,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>96</v>
+        <v>126</v>
       </c>
       <c r="C105">
         <v>761</v>
@@ -8804,7 +9274,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>97</v>
+        <v>127</v>
       </c>
       <c r="C106">
         <v>690</v>
@@ -8878,7 +9348,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>22</v>
+        <v>128</v>
       </c>
       <c r="C107">
         <v>574</v>
@@ -8952,7 +9422,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="C108">
         <v>774</v>
@@ -9026,7 +9496,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>86</v>
+        <v>130</v>
       </c>
       <c r="C109">
         <v>1100</v>
@@ -9100,7 +9570,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>87</v>
+        <v>131</v>
       </c>
       <c r="C110">
         <v>731</v>
@@ -9174,7 +9644,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>31</v>
+        <v>132</v>
       </c>
       <c r="C111">
         <v>872</v>
@@ -9248,7 +9718,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>22</v>
+        <v>133</v>
       </c>
       <c r="C112">
         <v>671</v>
@@ -9322,7 +9792,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="C113">
         <v>1094</v>
@@ -9396,7 +9866,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>100</v>
+        <v>135</v>
       </c>
       <c r="C114">
         <v>812</v>
@@ -9470,7 +9940,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>43</v>
+        <v>136</v>
       </c>
       <c r="C115">
         <v>1070</v>
@@ -9544,7 +10014,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>101</v>
+        <v>137</v>
       </c>
       <c r="C116">
         <v>939</v>
@@ -9618,7 +10088,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>102</v>
+        <v>138</v>
       </c>
       <c r="C117">
         <v>740</v>
@@ -9692,7 +10162,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>28</v>
+        <v>138</v>
       </c>
       <c r="C118">
         <v>614</v>
@@ -9766,7 +10236,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>28</v>
+        <v>139</v>
       </c>
       <c r="C119">
         <v>1095</v>
@@ -9840,7 +10310,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>43</v>
+        <v>140</v>
       </c>
       <c r="C120">
         <v>488</v>
@@ -9914,7 +10384,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>103</v>
+        <v>141</v>
       </c>
       <c r="C121">
         <v>869</v>
@@ -9988,7 +10458,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>104</v>
+        <v>142</v>
       </c>
       <c r="C122">
         <v>654</v>
@@ -10062,7 +10532,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="C123">
         <v>649</v>
@@ -10136,7 +10606,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>103</v>
+        <v>144</v>
       </c>
       <c r="C124">
         <v>1117</v>
@@ -10210,7 +10680,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>28</v>
+        <v>145</v>
       </c>
       <c r="C125">
         <v>818</v>
@@ -10284,7 +10754,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>15</v>
+        <v>146</v>
       </c>
       <c r="C126">
         <v>711</v>
@@ -10358,7 +10828,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>43</v>
+        <v>147</v>
       </c>
       <c r="C127">
         <v>814</v>
@@ -10432,7 +10902,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>106</v>
+        <v>148</v>
       </c>
       <c r="C128">
         <v>782</v>
@@ -10506,7 +10976,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>107</v>
+        <v>149</v>
       </c>
       <c r="C129">
         <v>1111</v>
@@ -10580,7 +11050,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>108</v>
+        <v>150</v>
       </c>
       <c r="C130">
         <v>926</v>
@@ -10654,7 +11124,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="C131">
         <v>921</v>
@@ -10728,7 +11198,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>110</v>
+        <v>152</v>
       </c>
       <c r="C132">
         <v>876</v>
@@ -10802,7 +11272,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>111</v>
+        <v>153</v>
       </c>
       <c r="C133">
         <v>737</v>
@@ -10876,7 +11346,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>112</v>
+        <v>154</v>
       </c>
       <c r="C134">
         <v>825</v>
@@ -10950,7 +11420,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="C135">
         <v>616</v>
@@ -11024,7 +11494,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>56</v>
+        <v>156</v>
       </c>
       <c r="C136">
         <v>660</v>
@@ -11098,7 +11568,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C137">
         <v>641</v>
@@ -11172,7 +11642,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="C138">
         <v>510</v>
@@ -11246,7 +11716,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>86</v>
+        <v>159</v>
       </c>
       <c r="C139">
         <v>662</v>
@@ -11320,7 +11790,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="C140">
         <v>648</v>
@@ -11394,7 +11864,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="C141">
         <v>823</v>
@@ -11468,7 +11938,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="C142">
         <v>798</v>
@@ -11542,7 +12012,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>43</v>
+        <v>162</v>
       </c>
       <c r="C143">
         <v>1213</v>
@@ -11616,7 +12086,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>43</v>
+        <v>163</v>
       </c>
       <c r="C144">
         <v>1067</v>
@@ -11690,7 +12160,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>117</v>
+        <v>164</v>
       </c>
       <c r="C145">
         <v>749</v>
@@ -11764,7 +12234,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>118</v>
+        <v>165</v>
       </c>
       <c r="C146">
         <v>559</v>
@@ -11838,7 +12308,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>119</v>
+        <v>166</v>
       </c>
       <c r="C147">
         <v>712</v>
@@ -11912,7 +12382,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="C148">
         <v>983</v>
@@ -11986,7 +12456,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>44</v>
+        <v>168</v>
       </c>
       <c r="C149">
         <v>1064</v>
@@ -12060,7 +12530,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="C150">
         <v>1114</v>
@@ -12134,7 +12604,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>122</v>
+        <v>170</v>
       </c>
       <c r="C151">
         <v>693</v>
@@ -12208,7 +12678,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>12</v>
+        <v>171</v>
       </c>
       <c r="C152">
         <v>1068</v>
@@ -12282,7 +12752,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="C153">
         <v>417</v>
@@ -12356,7 +12826,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="C154">
         <v>1249</v>
@@ -12430,7 +12900,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>103</v>
+        <v>174</v>
       </c>
       <c r="C155">
         <v>499</v>
@@ -12504,7 +12974,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>125</v>
+        <v>175</v>
       </c>
       <c r="C156">
         <v>787</v>
@@ -12578,7 +13048,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="C157">
         <v>871</v>
@@ -12652,7 +13122,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>116</v>
+        <v>177</v>
       </c>
       <c r="C158">
         <v>635</v>
@@ -12726,7 +13196,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>44</v>
+        <v>178</v>
       </c>
       <c r="C159">
         <v>899</v>
@@ -12800,7 +13270,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>9</v>
+        <v>179</v>
       </c>
       <c r="C160">
         <v>698</v>
@@ -12874,7 +13344,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>10</v>
+        <v>180</v>
       </c>
       <c r="C161">
         <v>876</v>
@@ -12948,7 +13418,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>99</v>
+        <v>181</v>
       </c>
       <c r="C162">
         <v>1058</v>
@@ -13022,7 +13492,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>100</v>
+        <v>182</v>
       </c>
       <c r="C163">
         <v>1072</v>
@@ -13096,7 +13566,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>127</v>
+        <v>183</v>
       </c>
       <c r="C164">
         <v>1076</v>
@@ -13170,7 +13640,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>7</v>
+        <v>184</v>
       </c>
       <c r="C165">
         <v>534</v>
@@ -13244,7 +13714,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>128</v>
+        <v>185</v>
       </c>
       <c r="C166">
         <v>950</v>
@@ -13318,7 +13788,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="C167">
         <v>573</v>
@@ -13392,7 +13862,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>122</v>
+        <v>185</v>
       </c>
       <c r="C168">
         <v>1015</v>
@@ -13466,7 +13936,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>129</v>
+        <v>186</v>
       </c>
       <c r="C169">
         <v>997</v>
@@ -13540,7 +14010,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>22</v>
+        <v>187</v>
       </c>
       <c r="C170">
         <v>948</v>
@@ -13614,7 +14084,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>130</v>
+        <v>188</v>
       </c>
       <c r="C171">
         <v>1024</v>
@@ -13688,7 +14158,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>42</v>
+        <v>188</v>
       </c>
       <c r="C172">
         <v>575</v>
@@ -13762,7 +14232,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>23</v>
+        <v>189</v>
       </c>
       <c r="C173">
         <v>575</v>
@@ -13836,7 +14306,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>99</v>
+        <v>190</v>
       </c>
       <c r="C174">
         <v>787</v>
@@ -13910,7 +14380,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>100</v>
+        <v>191</v>
       </c>
       <c r="C175">
         <v>772</v>
@@ -13984,7 +14454,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>131</v>
+        <v>192</v>
       </c>
       <c r="C176">
         <v>811</v>
@@ -14058,7 +14528,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>132</v>
+        <v>193</v>
       </c>
       <c r="C177">
         <v>730</v>
@@ -14132,7 +14602,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>28</v>
+        <v>194</v>
       </c>
       <c r="C178">
         <v>305</v>
@@ -14206,7 +14676,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="C179">
         <v>818</v>
@@ -14280,7 +14750,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>28</v>
+        <v>196</v>
       </c>
       <c r="C180">
         <v>688</v>
@@ -14354,7 +14824,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>50</v>
+        <v>197</v>
       </c>
       <c r="C181">
         <v>671</v>
@@ -14428,7 +14898,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>51</v>
+        <v>198</v>
       </c>
       <c r="C182">
         <v>619</v>
@@ -14502,7 +14972,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>88</v>
+        <v>199</v>
       </c>
       <c r="C183">
         <v>1203</v>
@@ -14576,7 +15046,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>89</v>
+        <v>200</v>
       </c>
       <c r="C184">
         <v>854</v>
@@ -14650,7 +15120,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>28</v>
+        <v>201</v>
       </c>
       <c r="C185">
         <v>735</v>
@@ -14724,7 +15194,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>133</v>
+        <v>202</v>
       </c>
       <c r="C186">
         <v>1058</v>
@@ -14798,7 +15268,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>134</v>
+        <v>203</v>
       </c>
       <c r="C187">
         <v>953</v>
@@ -14872,7 +15342,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>135</v>
+        <v>204</v>
       </c>
       <c r="C188">
         <v>1060</v>
@@ -14946,7 +15416,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>136</v>
+        <v>204</v>
       </c>
       <c r="C189">
         <v>543</v>
@@ -15020,7 +15490,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>28</v>
+        <v>204</v>
       </c>
       <c r="C190">
         <v>662</v>
@@ -15094,7 +15564,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="C191">
         <v>1078</v>
@@ -15168,7 +15638,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>138</v>
+        <v>204</v>
       </c>
       <c r="C192">
         <v>972</v>
@@ -15242,7 +15712,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>139</v>
+        <v>205</v>
       </c>
       <c r="C193">
         <v>973</v>
@@ -15316,7 +15786,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>140</v>
+        <v>206</v>
       </c>
       <c r="C194">
         <v>929</v>
@@ -15390,7 +15860,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>141</v>
+        <v>207</v>
       </c>
       <c r="C195">
         <v>1135</v>
@@ -15464,7 +15934,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>142</v>
+        <v>208</v>
       </c>
       <c r="C196">
         <v>1200</v>
@@ -15538,7 +16008,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>143</v>
+        <v>209</v>
       </c>
       <c r="C197">
         <v>792</v>
@@ -15612,7 +16082,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>144</v>
+        <v>210</v>
       </c>
       <c r="C198">
         <v>697</v>
@@ -15686,7 +16156,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="C199">
         <v>1114</v>
@@ -15760,7 +16230,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>146</v>
+        <v>212</v>
       </c>
       <c r="C200">
         <v>1008</v>
@@ -15834,7 +16304,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>147</v>
+        <v>213</v>
       </c>
       <c r="C201">
         <v>1103</v>
@@ -15908,7 +16378,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>148</v>
+        <v>213</v>
       </c>
       <c r="C202">
         <v>980</v>
@@ -15982,7 +16452,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>149</v>
+        <v>213</v>
       </c>
       <c r="C203">
         <v>1080</v>
@@ -16056,7 +16526,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>150</v>
+        <v>213</v>
       </c>
       <c r="C204">
         <v>995</v>
@@ -16130,7 +16600,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>151</v>
+        <v>213</v>
       </c>
       <c r="C205">
         <v>738</v>
@@ -16204,7 +16674,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>152</v>
+        <v>214</v>
       </c>
       <c r="C206">
         <v>972</v>
@@ -16278,7 +16748,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>153</v>
+        <v>215</v>
       </c>
       <c r="C207">
         <v>1120</v>
@@ -16352,7 +16822,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
       <c r="C208">
         <v>897</v>
@@ -16426,7 +16896,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="C209">
         <v>1134</v>
@@ -16500,7 +16970,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="C210">
         <v>820</v>
@@ -16574,7 +17044,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="C211">
         <v>1181</v>
@@ -16648,7 +17118,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="C212">
         <v>999</v>
@@ -16722,7 +17192,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="C213">
         <v>807</v>
@@ -16796,7 +17266,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="C214">
         <v>956</v>
@@ -16870,7 +17340,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="C215">
         <v>1106</v>
@@ -16944,7 +17414,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="C216">
         <v>1149</v>
@@ -17018,7 +17488,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="C217">
         <v>1158</v>
@@ -17092,7 +17562,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="C218">
         <v>1094</v>
@@ -17166,7 +17636,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>165</v>
+        <v>226</v>
       </c>
       <c r="C219">
         <v>1166</v>
@@ -17240,7 +17710,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="C220">
         <v>1185</v>
@@ -17314,7 +17784,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>167</v>
+        <v>228</v>
       </c>
       <c r="C221">
         <v>1054</v>
@@ -17388,7 +17858,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>47</v>
+        <v>229</v>
       </c>
       <c r="C222">
         <v>1193</v>
@@ -17462,7 +17932,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>48</v>
+        <v>230</v>
       </c>
       <c r="C223">
         <v>1194</v>
@@ -17536,7 +18006,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>49</v>
+        <v>231</v>
       </c>
       <c r="C224">
         <v>1213</v>
@@ -17610,7 +18080,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>168</v>
+        <v>232</v>
       </c>
       <c r="C225">
         <v>1168</v>
@@ -17684,7 +18154,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>169</v>
+        <v>233</v>
       </c>
       <c r="C226">
         <v>1249</v>
@@ -17758,7 +18228,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>170</v>
+        <v>234</v>
       </c>
       <c r="C227">
         <v>1198</v>
@@ -17832,7 +18302,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>171</v>
+        <v>235</v>
       </c>
       <c r="C228">
         <v>991</v>
@@ -17906,7 +18376,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>172</v>
+        <v>236</v>
       </c>
       <c r="C229">
         <v>1250</v>
@@ -17980,7 +18450,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>173</v>
+        <v>237</v>
       </c>
       <c r="C230">
         <v>978</v>
@@ -18054,7 +18524,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>44</v>
+        <v>238</v>
       </c>
       <c r="C231">
         <v>917</v>
@@ -18128,7 +18598,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>174</v>
+        <v>239</v>
       </c>
       <c r="C232">
         <v>1041</v>
@@ -18202,7 +18672,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>28</v>
+        <v>240</v>
       </c>
       <c r="C233">
         <v>548</v>
@@ -18276,7 +18746,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>175</v>
+        <v>241</v>
       </c>
       <c r="C234">
         <v>707</v>
@@ -18350,7 +18820,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="C235">
         <v>853</v>
@@ -18424,7 +18894,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>23</v>
+        <v>243</v>
       </c>
       <c r="C236">
         <v>810</v>
@@ -18498,7 +18968,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>177</v>
+        <v>244</v>
       </c>
       <c r="C237">
         <v>890</v>
@@ -18572,7 +19042,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>43</v>
+        <v>245</v>
       </c>
       <c r="C238">
         <v>1163</v>
@@ -18646,7 +19116,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>31</v>
+        <v>246</v>
       </c>
       <c r="C239">
         <v>1173</v>
@@ -18720,7 +19190,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>178</v>
+        <v>247</v>
       </c>
       <c r="C240">
         <v>900</v>
@@ -18794,7 +19264,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>44</v>
+        <v>248</v>
       </c>
       <c r="C241">
         <v>718</v>
@@ -18868,7 +19338,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>43</v>
+        <v>249</v>
       </c>
       <c r="C242">
         <v>893</v>
@@ -18942,7 +19412,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>179</v>
+        <v>250</v>
       </c>
       <c r="C243">
         <v>949</v>
@@ -19016,7 +19486,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>76</v>
+        <v>251</v>
       </c>
       <c r="C244">
         <v>1017</v>
@@ -19090,7 +19560,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>77</v>
+        <v>252</v>
       </c>
       <c r="C245">
         <v>1161</v>
@@ -19164,7 +19634,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>43</v>
+        <v>253</v>
       </c>
       <c r="C246">
         <v>1065</v>
@@ -19238,7 +19708,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>180</v>
+        <v>254</v>
       </c>
       <c r="C247">
         <v>1023</v>
@@ -19312,7 +19782,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>181</v>
+        <v>255</v>
       </c>
       <c r="C248">
         <v>1142</v>
@@ -19386,7 +19856,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>182</v>
+        <v>256</v>
       </c>
       <c r="C249">
         <v>1153</v>
@@ -19460,7 +19930,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>183</v>
+        <v>257</v>
       </c>
       <c r="C250">
         <v>658</v>
@@ -19534,7 +20004,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>184</v>
+        <v>258</v>
       </c>
       <c r="C251">
         <v>820</v>
@@ -19608,7 +20078,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>185</v>
+        <v>259</v>
       </c>
       <c r="C252">
         <v>1113</v>
@@ -19682,7 +20152,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>44</v>
+        <v>260</v>
       </c>
       <c r="C253">
         <v>405</v>
@@ -19756,7 +20226,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>43</v>
+        <v>261</v>
       </c>
       <c r="C254">
         <v>637</v>
@@ -19830,7 +20300,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>9</v>
+        <v>262</v>
       </c>
       <c r="C255">
         <v>682</v>
@@ -19904,7 +20374,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>10</v>
+        <v>263</v>
       </c>
       <c r="C256">
         <v>660</v>
@@ -19978,7 +20448,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>9</v>
+        <v>264</v>
       </c>
       <c r="C257">
         <v>803</v>
@@ -20052,7 +20522,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>10</v>
+        <v>265</v>
       </c>
       <c r="C258">
         <v>473</v>
@@ -20126,7 +20596,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>110</v>
+        <v>266</v>
       </c>
       <c r="C259">
         <v>830</v>
@@ -20200,7 +20670,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>111</v>
+        <v>267</v>
       </c>
       <c r="C260">
         <v>524</v>
@@ -20274,7 +20744,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>99</v>
+        <v>268</v>
       </c>
       <c r="C261">
         <v>643</v>
@@ -20348,7 +20818,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>100</v>
+        <v>269</v>
       </c>
       <c r="C262">
         <v>638</v>
@@ -20422,7 +20892,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>186</v>
+        <v>270</v>
       </c>
       <c r="C263">
         <v>682</v>
@@ -20496,7 +20966,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>187</v>
+        <v>271</v>
       </c>
       <c r="C264">
         <v>703</v>
@@ -20570,7 +21040,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>188</v>
+        <v>272</v>
       </c>
       <c r="C265">
         <v>641</v>
@@ -20644,7 +21114,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>116</v>
+        <v>273</v>
       </c>
       <c r="C266">
         <v>1201</v>
@@ -20718,7 +21188,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>28</v>
+        <v>274</v>
       </c>
       <c r="C267">
         <v>846</v>
@@ -20792,7 +21262,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>189</v>
+        <v>275</v>
       </c>
       <c r="C268">
         <v>710</v>
@@ -20866,7 +21336,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>4</v>
+        <v>276</v>
       </c>
       <c r="C269">
         <v>635</v>
@@ -20940,7 +21410,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>103</v>
+        <v>277</v>
       </c>
       <c r="C270">
         <v>588</v>
@@ -21014,7 +21484,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>28</v>
+        <v>278</v>
       </c>
       <c r="C271">
         <v>840</v>
@@ -21088,7 +21558,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>190</v>
+        <v>279</v>
       </c>
       <c r="C272">
         <v>954</v>
@@ -21162,7 +21632,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>191</v>
+        <v>280</v>
       </c>
       <c r="C273">
         <v>968</v>
@@ -21236,7 +21706,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>192</v>
+        <v>281</v>
       </c>
       <c r="C274">
         <v>841</v>
@@ -21310,7 +21780,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>56</v>
+        <v>281</v>
       </c>
       <c r="C275">
         <v>841</v>
@@ -21384,7 +21854,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>57</v>
+        <v>282</v>
       </c>
       <c r="C276">
         <v>804</v>
@@ -21458,7 +21928,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>44</v>
+        <v>283</v>
       </c>
       <c r="C277">
         <v>1150</v>
@@ -21532,7 +22002,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>28</v>
+        <v>283</v>
       </c>
       <c r="C278">
         <v>885</v>
@@ -21606,7 +22076,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>22</v>
+        <v>284</v>
       </c>
       <c r="C279">
         <v>1151</v>
@@ -21680,7 +22150,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>23</v>
+        <v>285</v>
       </c>
       <c r="C280">
         <v>1000</v>
@@ -21754,7 +22224,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>103</v>
+        <v>286</v>
       </c>
       <c r="C281">
         <v>882</v>
@@ -21828,7 +22298,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>38</v>
+        <v>287</v>
       </c>
       <c r="C282">
         <v>976</v>
@@ -21902,7 +22372,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>39</v>
+        <v>288</v>
       </c>
       <c r="C283">
         <v>816</v>
@@ -21976,7 +22446,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>193</v>
+        <v>289</v>
       </c>
       <c r="C284">
         <v>1073</v>
@@ -22050,7 +22520,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>194</v>
+        <v>290</v>
       </c>
       <c r="C285">
         <v>713</v>
@@ -22124,7 +22594,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>40</v>
+        <v>291</v>
       </c>
       <c r="C286">
         <v>787</v>
@@ -22198,7 +22668,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>41</v>
+        <v>292</v>
       </c>
       <c r="C287">
         <v>745</v>
@@ -22272,7 +22742,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>15</v>
+        <v>293</v>
       </c>
       <c r="C288">
         <v>588</v>
@@ -22346,7 +22816,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>103</v>
+        <v>294</v>
       </c>
       <c r="C289">
         <v>603</v>
@@ -22420,7 +22890,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>195</v>
+        <v>295</v>
       </c>
       <c r="C290">
         <v>657</v>
@@ -22494,7 +22964,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>103</v>
+        <v>296</v>
       </c>
       <c r="C291">
         <v>691</v>
@@ -22568,7 +23038,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>43</v>
+        <v>297</v>
       </c>
       <c r="C292">
         <v>497</v>
@@ -22642,7 +23112,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>88</v>
+        <v>297</v>
       </c>
       <c r="C293">
         <v>935</v>
@@ -22716,7 +23186,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>89</v>
+        <v>298</v>
       </c>
       <c r="C294">
         <v>875</v>
@@ -22790,7 +23260,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>103</v>
+        <v>299</v>
       </c>
       <c r="C295">
         <v>737</v>
@@ -22864,7 +23334,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>27</v>
+        <v>220</v>
       </c>
       <c r="C296">
         <v>726</v>
@@ -22938,7 +23408,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>122</v>
+        <v>300</v>
       </c>
       <c r="C297">
         <v>853</v>
@@ -23012,7 +23482,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>122</v>
+        <v>300</v>
       </c>
       <c r="C298">
         <v>808</v>
@@ -23086,7 +23556,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>128</v>
+        <v>291</v>
       </c>
       <c r="C299">
         <v>1230</v>
@@ -23160,7 +23630,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>128</v>
+        <v>291</v>
       </c>
       <c r="C300">
         <v>477</v>
@@ -23234,7 +23704,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>86</v>
+        <v>301</v>
       </c>
       <c r="C301">
         <v>711</v>
@@ -23308,7 +23778,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>87</v>
+        <v>302</v>
       </c>
       <c r="C302">
         <v>680</v>
@@ -23382,7 +23852,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>21</v>
+        <v>302</v>
       </c>
       <c r="C303">
         <v>1040</v>
@@ -23456,7 +23926,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>196</v>
+        <v>303</v>
       </c>
       <c r="C304">
         <v>1110</v>
@@ -23530,7 +24000,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>197</v>
+        <v>304</v>
       </c>
       <c r="C305">
         <v>1185</v>
@@ -23604,7 +24074,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>194</v>
+        <v>304</v>
       </c>
       <c r="C306">
         <v>1108</v>
@@ -23678,7 +24148,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>198</v>
+        <v>304</v>
       </c>
       <c r="C307">
         <v>864</v>
@@ -23752,7 +24222,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>199</v>
+        <v>305</v>
       </c>
       <c r="C308">
         <v>927</v>
@@ -23826,7 +24296,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>200</v>
+        <v>305</v>
       </c>
       <c r="C309">
         <v>851</v>
@@ -23900,7 +24370,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>201</v>
+        <v>306</v>
       </c>
       <c r="C310">
         <v>814</v>
@@ -23974,7 +24444,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>202</v>
+        <v>307</v>
       </c>
       <c r="C311">
         <v>1059</v>
@@ -24048,7 +24518,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>99</v>
+        <v>308</v>
       </c>
       <c r="C312">
         <v>1032</v>
@@ -24122,7 +24592,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>100</v>
+        <v>309</v>
       </c>
       <c r="C313">
         <v>712</v>
@@ -24196,7 +24666,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>7</v>
+        <v>310</v>
       </c>
       <c r="C314">
         <v>934</v>
@@ -24270,7 +24740,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>28</v>
+        <v>311</v>
       </c>
       <c r="C315">
         <v>1139</v>
@@ -24344,7 +24814,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>203</v>
+        <v>312</v>
       </c>
       <c r="C316">
         <v>441</v>
@@ -24418,7 +24888,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>15</v>
+        <v>313</v>
       </c>
       <c r="C317">
         <v>931</v>
@@ -24492,7 +24962,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>76</v>
+        <v>314</v>
       </c>
       <c r="C318">
         <v>813</v>
@@ -24566,7 +25036,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>77</v>
+        <v>315</v>
       </c>
       <c r="C319">
         <v>737</v>
@@ -24640,7 +25110,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>204</v>
+        <v>316</v>
       </c>
       <c r="C320">
         <v>749</v>
@@ -24714,7 +25184,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>205</v>
+        <v>317</v>
       </c>
       <c r="C321">
         <v>654</v>
@@ -24788,7 +25258,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>206</v>
+        <v>318</v>
       </c>
       <c r="C322">
         <v>1064</v>
@@ -24862,7 +25332,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>207</v>
+        <v>319</v>
       </c>
       <c r="C323">
         <v>1054</v>
@@ -24936,7 +25406,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>208</v>
+        <v>320</v>
       </c>
       <c r="C324">
         <v>828</v>
@@ -25010,7 +25480,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>209</v>
+        <v>321</v>
       </c>
       <c r="C325">
         <v>981</v>
@@ -25084,7 +25554,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>210</v>
+        <v>322</v>
       </c>
       <c r="C326">
         <v>699</v>
@@ -25158,7 +25628,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>211</v>
+        <v>323</v>
       </c>
       <c r="C327">
         <v>689</v>
@@ -25232,7 +25702,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>212</v>
+        <v>324</v>
       </c>
       <c r="C328">
         <v>1124</v>
@@ -25306,7 +25776,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>128</v>
+        <v>325</v>
       </c>
       <c r="C329">
         <v>1124</v>
@@ -25380,7 +25850,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>43</v>
+        <v>326</v>
       </c>
       <c r="C330">
         <v>1096</v>
@@ -25454,7 +25924,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>213</v>
+        <v>327</v>
       </c>
       <c r="C331">
         <v>962</v>
@@ -25528,7 +25998,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>214</v>
+        <v>328</v>
       </c>
       <c r="C332">
         <v>912</v>
@@ -25602,7 +26072,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>187</v>
+        <v>329</v>
       </c>
       <c r="C333">
         <v>1205</v>
@@ -25676,7 +26146,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>188</v>
+        <v>330</v>
       </c>
       <c r="C334">
         <v>1054</v>
@@ -25750,7 +26220,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>124</v>
+        <v>331</v>
       </c>
       <c r="C335">
         <v>530</v>
@@ -25824,7 +26294,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>9</v>
+        <v>332</v>
       </c>
       <c r="C336">
         <v>1010</v>
@@ -25898,7 +26368,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>10</v>
+        <v>333</v>
       </c>
       <c r="C337">
         <v>1142</v>
@@ -25972,7 +26442,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>215</v>
+        <v>334</v>
       </c>
       <c r="C338">
         <v>1004</v>
@@ -26046,7 +26516,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>216</v>
+        <v>335</v>
       </c>
       <c r="C339">
         <v>899</v>
@@ -26120,7 +26590,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>217</v>
+        <v>336</v>
       </c>
       <c r="C340">
         <v>1111</v>
@@ -26194,7 +26664,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>218</v>
+        <v>337</v>
       </c>
       <c r="C341">
         <v>745</v>
@@ -26268,7 +26738,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>219</v>
+        <v>338</v>
       </c>
       <c r="C342">
         <v>618</v>
@@ -26342,7 +26812,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>220</v>
+        <v>339</v>
       </c>
       <c r="C343">
         <v>899</v>
@@ -26416,7 +26886,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>221</v>
+        <v>340</v>
       </c>
       <c r="C344">
         <v>885</v>
@@ -26490,7 +26960,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>222</v>
+        <v>341</v>
       </c>
       <c r="C345">
         <v>829</v>
@@ -26564,7 +27034,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>7</v>
+        <v>342</v>
       </c>
       <c r="C346">
         <v>1004</v>
@@ -26638,7 +27108,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>116</v>
+        <v>343</v>
       </c>
       <c r="C347">
         <v>977</v>
@@ -26712,7 +27182,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>223</v>
+        <v>344</v>
       </c>
       <c r="C348">
         <v>707</v>
@@ -26786,7 +27256,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>224</v>
+        <v>345</v>
       </c>
       <c r="C349">
         <v>754</v>
@@ -26860,7 +27330,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>136</v>
+        <v>346</v>
       </c>
       <c r="C350">
         <v>915</v>
@@ -26934,7 +27404,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>225</v>
+        <v>347</v>
       </c>
       <c r="C351">
         <v>859</v>
@@ -27008,7 +27478,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>226</v>
+        <v>348</v>
       </c>
       <c r="C352">
         <v>993</v>
@@ -27082,7 +27552,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>227</v>
+        <v>349</v>
       </c>
       <c r="C353">
         <v>989</v>
@@ -27156,7 +27626,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>124</v>
+        <v>350</v>
       </c>
       <c r="C354">
         <v>836</v>
@@ -27230,7 +27700,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>28</v>
+        <v>351</v>
       </c>
       <c r="C355">
         <v>690</v>
@@ -27304,7 +27774,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>124</v>
+        <v>352</v>
       </c>
       <c r="C356">
         <v>945</v>
